--- a/output/组分结构表_F版30篇_2026-10-31/组分结构表.xlsx
+++ b/output/组分结构表_F版30篇_2026-10-31/组分结构表.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="待你判断" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="看图核对" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="读原文判定" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="结构图（可选）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="组分表" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="别名表" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="未收录" sheetId="6" state="visible" r:id="rId6"/>
@@ -1490,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1532,34 +1532,34 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>待你判断</t>
+          <t>读原文判定</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>18 个问题，问的是“原文用的是不是这个分子”，不用懂 SMILES。在最后一列写同意，或写不同意和原因</t>
+          <t>20 行：原文只有缩写、名称写错、自合成、没有公共库记录等情况，Claude 读原文（含 PDF 里的结构图）后的判定，附原句。“剩余疑点”列非空的 3 行是原文自身矛盾或信息不全</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>要看，主要就这一页</t>
+          <t>不用逐条确认；有不同意见再在最后一列写</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>看图核对</t>
+          <t>结构图（可选）</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>A 档每个组分的结构图、一句话结构要点、原文全称句子、PubChem 链接（点开能看到同一分子的别名和结构）</t>
+          <t>A 档每个组分的结构图、一句话结构要点、原文全称句子、PubChem 链接；有的查看器不显示图片，图也在 结构图/ 文件夹</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>扫一眼；图和你认识的分子不一样就在最后一列写</t>
+          <t>不用看</t>
         </is>
       </c>
     </row>
@@ -1663,66 +1663,74 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>机器已经核过的：✅ 的写法同时满足两条——本篇原文里找到了全称，用这个全称去 PubChem 查到的结构和我们写的一致。剩下需要人判断的都写进了“待你判断”页。</t>
+          <t>✅ 的写法同时满足两条：本篇原文里找到了全称；用这个全称去 PubChem 查到的结构和我们写的一致（PubChem 没有的自合成分子，改用原文的结构图、合成路线和谱图核对）。🔶 是 Claude 读原文后判定的，依据见“读原文判定”页。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>同分异构体：分子式一样、结构不同的分子，SMILES 和 InChIKey 都不同，不会被当成同一个。本批就有两对：正己烷与 2,3-二甲基丁烷（都是 C₆H₁₄），PPEO-CF₃ 与 PXEO-CF₃（正丙基与异丙基，都是 C₇H₁₃F₃O₂）。所以身份按结构定，不按化学式定；用哪个异构体看原文全称（如 P510 写明 “n-hexane”“2,3 dimethylbutane”）。</t>
+          <t>原文没有结构图时怎么定结构：① 系统化学名本身就唯一确定结构（如 2,3-dimethylbutane），商品溶剂和盐大多靠这个；② CAS 号、供应商；③ 合成路线（原料＋反应推出产物，P386 的两个自合成醚就是这样核的，SI 的结构图只是再确认）；④ 核磁等谱图佐证；⑤ 只有缩写时，领域通用且语境一致（如“常规醚类电解液 1 M LiTFSI in DME:DOL”）按通用含义，标 🔶；缩写有歧义又没有全称时不猜，按“结构未公开”不收录。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>立体异构：PC、FEC 有一个手性碳，商品是两种构型各半的混合物，SMILES 不写构型标记，InChIKey 第二段为 UHFFFAOYSA（表示未指定立体）。以后原文若写明某一构型或顺/反式，再写构型标记，与混合物算不同组分。</t>
+          <t>同分异构体：分子式一样、结构不同的分子，SMILES 和 InChIKey 都不同，不会被当成同一个。本批就有两对：正己烷与 2,3-二甲基丁烷（都是 C₆H₁₄），PPEO-CF₃ 与 PXEO-CF₃（正丙基与异丙基，都是 C₇H₁₃F₃O₂）。所以身份按结构定，不按化学式定；用哪个异构体看原文全称（如 P510 写明 “n-hexane”“2,3 dimethylbutane”）。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>描述符怎么定的：分子量、原子数、环数、可旋转键数、TPSA、氢键受体数对任何分子都能算，以后不用改；官能团标签是按锂硫电解液常见类别预先定的，不是按这 30 篇定的（本批没有砜、P=O、腈，这几列都是 0）。全量提取出现新类别时加标签，只多一列，已有组分的其他数值不变。</t>
+          <t>立体异构：PC、FEC 有一个手性碳，商品是两种构型各半的混合物，SMILES 不写构型标记，InChIKey 第二段为 UHFFFAOYSA（表示未指定立体）。以后原文若写明某一构型或顺/反式，再写构型标记，与混合物算不同组分。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>覆盖检查：每次重跑都检查 A 档有没有组分一个标签都没命中（烃（没有极性官能团，这本身就是信息）和不含碳的无机盐/离子（组分身份本身就是特征）除外）。本次全部覆盖；10-31 这项检查查出 TFSI/FSI/OTf 等阴离子的磺酰基、苯乙胺/苄胺/季铵的氮没有标签，已补“磺酰基”“胺/铵氮”两列，另加 Cl/Br/I 原子数、芳环数。</t>
+          <t>描述符怎么定的：分子量、原子数、环数、可旋转键数、TPSA、氢键受体数对任何分子都能算，以后不用改；官能团标签是按锂硫电解液常见类别预先定的，不是按这 30 篇定的（本批没有砜、P=O、腈，这几列都是 0）。全量提取出现新类别时加标签，只多一列，已有组分的其他数值不变。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>描述符是结构特征，不等于配位强度、介电常数或溶解度。Morgan 指纹对小分子溶剂很粗：DME 与 DOL 同为醚，相似度却为 0，所以分类别看官能团标签，不看指纹。</t>
+          <t>覆盖检查：每次重跑都检查 A 档有没有组分一个标签都没命中（烃（没有极性官能团，这本身就是信息）和不含碳的无机盐/离子（组分身份本身就是特征）除外）。本次全部覆盖；10-31 这项检查查出 TFSI/FSI/OTf 等阴离子的磺酰基、苯乙胺/苄胺/季铵的氮没有标签，已补“磺酰基”“胺/铵氮”两列，另加 Cl/Br/I 原子数、芳环数。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>覆盖：组分条目 1257 条 → 对应到组分 1173 条，未收录（有原因）84 条，对不上 0 条。规则见方案 §5.8。</t>
+          <t>描述符是结构特征，不等于配位强度、介电常数或溶解度。Morgan 指纹对小分子溶剂很粗：DME 与 DOL 同为醚，相似度却为 0，所以分类别看官能团标签，不看指纹。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>覆盖：组分条目 1257 条 → 对应到组分 1173 条，未收录（有原因）84 条，对不上 0 条。规则见方案 §5.8。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>配方挂接与单位换算待 F 版 30 篇人工复核完成后进行；“顺带发现的提取问题_复核完再看.json”请在复核完成后再打开。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
@@ -1738,508 +1746,751 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>对象</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>论文</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>我的处理和理由</t>
+          <t>原文写法/组分</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>原文依据</t>
+          <t>核验</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>论文</t>
+          <t>Claude 的判定</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>你的判断✍（同意／不同意＋原因）</t>
+          <t>原文依据（句号与原句）</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>剩余疑点</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>有不同意见再写✍</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>组分结构</t>
+          <t>组分</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>「看图核对」页 乙二醇（2,2,2-三氟乙基）（正丙基）醚（PPEO_CF3）的结构图对吗？</t>
+          <t>P386</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>自合成，按原文化学名（P386 M0052）绘制，待确认；PubChem：PubChem 未收录</t>
+          <t>乙二醇（2,2,2-三氟乙基）（正丙基）醚（PPEO_CF3）</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>P386 [M0052] …Results and Discussion The synthesis route of ethylene glycol (2,2,2-trifluoroethyln-propyl) ether (PPEO-CF3) and ethylene glycol (2,2,2- trifluoroethyl-i-propyl) ether (PXEO-CF3) is displaye…</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>P386</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="n"/>
+          <t>结构与原文一致</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>P386 SI Figure S1 合成路线图画出的产物与此结构一致：2-丙氧基乙醇经对甲苯磺酰化，再与 2,2,2-三氟乙醇钠醚化（SI S0017–S0027）；Figure S2 ¹H NMR 共 13 个 H，与 C₇H₁₃F₃O₂ 一致</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>组分结构</t>
+          <t>组分</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>「看图核对」页 乙二醇（2,2,2-三氟乙基）（异丙基）醚（PXEO_CF3）的结构图对吗？</t>
+          <t>P386</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>自合成，按原文化学名（P386 M0052）绘制，待确认；PubChem：一致（CID 134171504）</t>
+          <t>乙二醇（2,2,2-三氟乙基）（异丙基）醚（PXEO_CF3）</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>P386 [M0052] …oute of ethylene glycol (2,2,2-trifluoroethyln-propyl) ether (PPEO-CF3) and ethylene glycol (2,2,2- trifluoroethyl-i-propyl) ether (PXEO-CF3) is displayed in Figure S1 and analyzed via nuclear magnetic resonance (NMR) test…</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>P386</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="n"/>
+          <t>结构与原文一致</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>P386 SI Figure S1 合成路线图画出的产物与此结构一致：同一路线，起始物换为 2-异丙氧基乙醇（SI S0028）</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>组分结构</t>
+          <t>组分</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>「看图核对」页 三碘化锂（LiI3）的结构图对吗？</t>
+          <t>P038</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>按化学式书写；P038 化学氧化测试液中按 2.5 mM 加入；PubChem：未查询（按化学式书写）</t>
+          <t>三碘化锂（LiI3）</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>P038 [M0007] …, Tsinghua University, Beijing 100084, China A R T I C L E I N F O Keywords: Lithium sulfide Indium triiodide Energy density Carbonized wipes Full cell A B S T R A C T Previous investigations have shown that h…</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>P038</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="n"/>
+          <t>结构与原文一致</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>P038 M0070 在 DOL/DME 中加入 2.5 mM LiI₃ 溶液，M0073 以 295、366 nm 两个吸收峰指认 I₃⁻：即 Li⁺ 与 I₃⁻</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr"/>
+      <c r="H4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>组分结构</t>
+          <t>组分</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Cu-2-T（氯桥双核铜配合物）（CU2T）没有单一结构，按前驱体记录、不算描述符，可以吗？</t>
+          <t>P380</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>金属配合物，在电解液中原位生成；原文 P380 M0031：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成。没有可靠的单一 SMILES，按前驱体记录身份，不算描述符；PubChem：无 SMILES</t>
+          <t>Cu-2-T（氯桥双核铜配合物）（CU2T）</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>P380 [M0003] …Herein, a chlorine bridge-enabled binuclear copper complex (Cu-2-T) is in situ synthesized in electrolyte as homogeneous catalyst for rationalizing the Li-S r…</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>P380</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="n"/>
+          <t>没有单一结构，不算描述符</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>金属配合物，没有可靠的单一 SMILES，不算 RDKit 描述符，分析时按“含 Cu-2-T”分块记录。原文 P380：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成（M0031），为双 Cl 桥连的双核 Cu 配合物（M0042）；与 KPF₆ 交换得 Cu-2-PF₆，再溶入 1 M LiTFSI＋2 wt% LiNO₃ 的 DME/DOL 中由 TFSI⁻ 置换得 Cu-2-T（M0040），为单 Cl 桥连的双核 Cu 配合物（M0043，Figure 1a 晶体结构，CCDC 2243502）</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>确切组成见 CCDC 晶体数据</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>原文写法</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>P137 的「Li[TFSA]」指的是双三氟甲磺酰亚胺锂吗？</t>
+          <t>P034</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>TFSA 与 TFSI 是同一阴离子的两种缩写</t>
+          <t>DMTS</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>[M0014] …onal ether-based electrolytes that dissolve PS, such as 1 M Li-bis(trifluoromethane sulfonyl)amide (Li[TFSA]) in 1,3-dioxolane/1,2-dimethoxyethane (DOL/DME), leads to degradation of battery performance.22,23…</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>P137</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="n"/>
+          <t>本篇原文未找到全称；全文只写缩写；M0060 与 dimethyl tetrasulfide (DMTtS)、DMDS 并列为二甲基多硫醚中间体，S0005 把 DMTS 加入电解液测 ¹H NMR，判为二甲基三硫醚</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>[M0060] …According to our previous NMR results [37], the DMPS intermediates are mainly composed of DMTS and dimethyl tertrasulfide (DMTtS), which, upon complete reduction involve the transfer of 4 and 3 eper sulfur reacting with DMDS, or a maximum specific capacity of 3350 and 2515 mAh g-1 based on solid sulfur in the cathode, respectively.…
+[S0005] …Wang) Figure S1. 1H NMR spectra of conventional electrolyte with added DMTS (10 mg DMTS in 2.5 mL electrolyte) discharged with a sulfur-free OMC cathode, showing the disappear of DMTS peak (~2.50 ppm) and formation of a new peak at 2.34 ppm ascribed to dissolved CH3SSLi, similar to the position of DMDS, at 50% depths of discharge (DOD).…</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr"/>
+      <c r="H6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>原文写法</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>P160 的「DME」指的是1,2-二甲氧基乙烷吗？</t>
+          <t>P038</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>原文 M0024 写作“1,2-dimethoxymethane (DME)”，名称有误，按 1,2-二甲氧基乙烷处理</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>[M0024] …es of lithium-sulfur batteries are mainly composed of 1,3-dioxolane (DOL) and 1,2-dimethoxymethane (DME).…</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>P160</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="n"/>
+          <t>本篇原文未找到全称；原文 M0214 全称写作“1,2-dioxolane (DOL)”，位次有误：1,2-二氧戊环是另一种异构体（环状过氧化物），不作电解液溶剂；本篇其余各处都是“1 M LiTFSI in DOL/DME with 1 wt% LiNO3”标准醚类电解液（M0060、M0079、S0014），判为 1,3-二氧戊环</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>[M0214] …The electrolyte containing 1 M bis(trifluoromethane) sulfonamide lithium (LiTFSI)/1,2-dioxolane (DOL): dimethoxyethane (DME) (1:1 by volume) with 1 wt% LiNO3 and 150 mM LiI or 50 mM InI3 additives was firstly injected to infiltrate the separator, which was pre-covered on the top of the SnO2 anode.…
+[M0060] …Electrochemical performance of Li/Li2S and SnO2/Li2S batteries In this section, to investigate the effective role of InI3 additive in activating Li2S cathode, we assembled the Li/Li2S half cells employing Li anode, Li2S cathode and ether-based electrolyte (1 M LiTFSI in DOL/ DME with 1 wt% LiNO3) with 150 mM LiI or 50 mM InI3 additive.…
+[S0014] …Figure S2 Rate and cycling tests of Li/Li2S batteries and Li/Li2S8 batteries employing standard ether-based electrolyte (1 M LiTFSI in DOL/DME with 1 wt. % LiNO3).…</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>原文写法</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>P169 的「DIOX」指的是1,3-二氧戊环吗？</t>
+          <t>P137</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>本篇 DIOX 指 1,3-二氧戊环（M0009），不是 1,4-二氧六环</t>
+          <t>Li[TFSA]</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>[M0009] …luoromethanesulfonyl)imide (LiTFSI) salt solution in distilled dimethoxyethane (DME)/1,3-dioxolane (DIOX) (1:1, v/v) solvent with 1-2 wt. % of LiNO3 additive.9-11 The reduction of S typically proceeds thr…</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>P169</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="n"/>
+          <t>TFSA 与 TFSI 是同一阴离子的两种缩写；P137 M0014 写明 Li-bis(trifluoromethane sulfonyl)amide (Li[TFSA])</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>[M0014] …more, reducing the amount of conventional ether-based electrolytes that dissolve PS, such as 1 M Li-bis(trifluoromethane sulfonyl)amide (Li[TFSA]) in 1,3-dioxolane/1,2-dimethoxyethane (DOL/DME), leads to degradation of battery performa…</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr"/>
+      <c r="H8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>原文写法</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>P334 的「DME」指的是1,2-二甲氧基乙烷吗？</t>
+          <t>P160</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>原文 M0169 写作“1, 2-dimethoxythane (DME)”，拼写有误，按 1,2-二甲氧基乙烷处理</t>
+          <t>DME</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>[M0169] …Aladdin, 99.9 %) and 2 wt% LiNO3 (Aladdin, 99.9 %) in the mixture solvent with 1, 2-dimethoxythane (DME, Aladdin, 99.5 %) and 1, 3-dioxolane (DOL, Aladdin, 99.5 %) (v/ Fig. 5.…</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>P334</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="n"/>
+          <t>本篇原文未找到全称；原文 M0024 写“1,2-dimethoxymethane (DME)”，这个名称不成立（甲烷只有一个碳，不会有 1,2 位）；M0025 写 DME 沸点 42 °C，这是二甲氧基甲烷（甲缩醛）的沸点，1,2-二甲氧基乙烷为 85 °C。但对照电解液是锂硫标准的“1 M LiTFSI/DOL+DME（1:1）”（S0008），M0048 引用的 Suo 等 7 M LiTFSI-DOL:DME 也是 1,2-二甲氧基乙烷，判为 1,2-二甲氧基乙烷</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>[M0024] …As is known to all, the widely used electrolytes of lithium-sulfur batteries are mainly composed of 1,3-dioxolane (DOL) and 1,2-dimethoxymethane (DME).…
+[M0025] …However, relatively low boiling points (75 °C for DOL and 42 °C for DME) may lead to cell failure or hazardous safety events.…
+[M0048] …Suo et al. developed a new class of ultrahigh salt concentration electrolyte (7 mol LiTFSI to DOL:DME (1:1 by volume)) to effectively suppress the growth of lithium dendrites and inhibit the shuttling effect of polysulfides of lithium-sulfur batteries [47] .…
+[S0008] …S1 Flame-retardant characteristics of 1 M LiTFSI/DOL+DME (V:V=1:1).…</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>原文名称和沸点都指向二甲氧基甲烷，只能按语境判定；要确证只能问作者</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>原文写法</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>P380 的「PF6−（反离子未报告）」指的是六氟磷酸根吗？</t>
+          <t>P169</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>原文未报告反离子</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr"/>
+          <t>DIOX</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>P380</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="n"/>
+          <t>M0009 写明 1,3-dioxolane (DIOX)；DIOX 常指 1,4-二氧六环，本篇不是</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>[M0009] …With one of the highest theoretical capacities (1675 mAh·g-1) of any conversion-type cathode, the pursuit of long-lasting and stable Li-S batteries remains a global research focus for the past decade.2,3,6-8 In the Li-S conversion chemistry studies, the most commonly used electrolyte comprises ∼1 M lithium bis- (trifluoromethanesulfonyl)imide (LiTFSI) salt solution in distilled dimethoxyethane (DME)/1,3-dioxolane (DIOX) (1:1, v/v) solvent with 1-2 wt. % of LiNO3 additive.9-11 The reduction of S typically proceeds through a formation of a series of polysulfide species, which are for the most part soluble in common organic solvents and electrolytes.…</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr"/>
+      <c r="H10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>原文写法</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>P536 的「tetraglyme / tetracarboxylic ester」指的是四乙二醇二甲醚吗？</t>
+          <t>P334</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>同一液体原文两种写法：M0206 写 tetraglyme，S0018 写 tetracarboxylic ester；按 tetraglyme 处理，待确认</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr"/>
+          <t>DME</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>P536</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="n"/>
+          <t>本篇原文未找到全称；原文 M0169 写“1, 2-dimethoxythane (DME, Aladdin, 99.5 %)”，少一个 e，判为 1,2-二甲氧基乙烷</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>[M0169] …Preparation of electrolytes The base electrolyte is 1 M lithium bis(trifluoromethanesulf ony)imide (LiTFSI, Aladdin, 99.9 %) and 2 wt% LiNO3 (Aladdin, 99.9 %) in the mixture solvent with 1, 2-dimethoxythane (DME, Aladdin, 99.5 %) and 1, 3-dioxolane (DOL, Aladdin, 99.5 %) (v/ Fig. 5.…</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr"/>
+      <c r="H11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>只写缩写</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>P034 只写了「DMTS」，按二甲基三硫醚（dimethyl trisulfide）处理，可以吗？</t>
+          <t>P380</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>领域通用含义；另有 2 篇写了全称（P062、P156），结构与 PubChem 一致</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr"/>
+          <t>PF6−（反离子未报告）</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>P034</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="n"/>
+          <t>P380 中 PF₆⁻ 来自 KPF₆ 阴离子交换得到的 Cu-2-PF₆（M0033、M0040），平衡离子是 Cu-2 配合物阳离子，溶入电解液后被 TFSI⁻ 置换</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>[M0033] …Accordingly, Cu-2 powder and potassium hexafluorophosphate (KPF6) react in deionized water and the attained product is subsequently dissolved in the commercial electrolyte for obtaining the final Cu-2-T.…
+[M0040] …The homogeneous catalyst of Cu-2-T was synthesized by experiencing the stepwise replacement procedures: i) KPF6 was first used to occur anion replacement reaction with Cu-2 in deionized water to generate the precipitation of Cu-2-PF6; ii) the Cu-2-PF6 after drying was dissolved in the mixture of DME/DOL containing 1.0 mol L-1 LiTFSI and 2 wt% LiNO3 to be replaced by TFSI-.…</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr"/>
+      <c r="H12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>只写缩写</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>P038、P141、P160、P334、P380、P558、P627 只写了「LiTFSI、LiTFSI（正极液）」，按双三氟甲磺酰亚胺锂（lithium bis(trifluoromethanesulfonyl)imide）处理，可以吗？</t>
+          <t>P386</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>领域通用含义；另有 15 篇写了全称（P034、P054、P062、P113、P156、P169、P218、P307、P315、P323、P425、P510、P536、P609、P668），结构与 PubChem 一致</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr"/>
+          <t>LiFSI</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>P038、P141、P160、P334、P380、P558、P627</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="n"/>
+          <t>本篇原文未找到全称；全文只写缩写；S0029 写 LiFSI 购自 Tansoole，M0174 写富 LiF 主要来自 LiFSI 盐，按双氟磺酰亚胺锂</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>[S0029] …Electrolyte preparation and characterization The LiFSI and DME were purchased from Tansoole and the solvent was further purified with a Li+ exchange 4 Å molecular sieve for 24 h. 2 M LiFSI was dissolved in different solvents to prepare electrolytes marked in 2 M-DME, 2 M-PPEO-CF3 and 2 M-PXEO-CF3 respectively.…
+[M0174] …Rich LiF can be observed which mainly originates from the LiFSI salt owing to the solvation structure with abundant AGGs.[26] The C 1s spectrum reveals higher content of C  O than C=O species, indicating the formation of polyether, which may ascribe to the active A-H in the methine of PXEO-CF3 according to our previous work.[22] Moreover, the Li 1s spectrum displays two peaks at 53.9 and 55.4 eV respectively, corresponding to Li2O and LiF/R-OLi.[18,27] The interphase rich in Li2O is also demonstrated via O 1s spectrum.…</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr"/>
+      <c r="H13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>只写缩写</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>P386、P633 只写了「LiFSI」，按双氟磺酰亚胺锂（lithium bis(fluorosulfonyl)imide）处理，可以吗？</t>
+          <t>P536</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>领域通用含义；另有 5 篇写了全称（P215、P309、P425、P451、P609），结构与 PubChem 一致</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr"/>
+          <t>tetraglyme / tetracarboxylic ester</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>P386、P633</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="n"/>
+          <t>主文 M0206 图注写 Li||Li2S8/tetraglyme；SI S0018 同一实验写“tetracarboxylic ester”，这不是常用电解液溶剂的名称，判为 SI 笔误，按四乙二醇二甲醚</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>[M0206] …The sulfur cathode after 50 cycles at 0.2C lithium‑sulfur battery with PBQ at (a-c) different magnifications (vertical views of the cathode), and with MCBQ at (d-f) different magnifications; cross-sectional view of the sulfur cathode with (g) PBQ and (h) MCBQ; (d-f) Potentiostatic discharge curves of Li||Li2S8/tetraglyme cells at a potential of 2.05 V.…
+[S0018] …Specifically, 20 μL of a 0.2 M Li2S8/tetracarboxylic ester electrolyte solution was added to the working electrode side, while an identical volume of blank electrolyte without Li2S8 was applied to the counter electrode (anode) side.…</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>SI 与主文写法不一致，以主文为准</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>只写缩写</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>P594 只写了「DEC」，按碳酸二乙酯（diethyl carbonate）处理，可以吗？</t>
+          <t>P594</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>领域通用含义</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr"/>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>P594</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="n"/>
+          <t>本篇原文未找到全称；全文只写缩写；M0031 写常规碳酸酯电解液，M0069 中 DEC 与 EC、PF₆⁻ 并列，判为碳酸二乙酯</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>[M0031] …In this work, we introduce an anion-transfer functional electrolyte that incorporates non-consumable tetramethylammonium (TMA) bromide as an additive in a conventional carbonate electrolyte to regulate the local coordination environment and interfacial chemistry of Li|SPAN batteries.…
+[M0069] …In both electrolytes, sharp primary solvation peaks for Li+ paired with O(EC), O(DEC), and F(PF6 - ) consistently appeared near 2.0 Å, indicating that the primary Li+ solvation shell remained intact.…</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr"/>
+      <c r="H15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>只写缩写</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>P627 只写了「DME」，按1,2-二甲氧基乙烷（1,2-dimethoxyethane）处理，可以吗？</t>
+          <t>P627</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>领域通用含义；另有 26 篇写了全称（P034、P038、P054、P062、P102、P113、P137、P141、P156、P169、P215、P218、P307、P309、P315、P323、P380、P386、P425、P451、P510、P536、P558、P609、P633、P668），结构与 PubChem 一致</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr"/>
+          <t>DME</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>P627</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="n"/>
+          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>[M0074] …Two cells of each polysulfide were prepared, one containing conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v)) and another containing LP30 in order to analyze the interaction of polysulfide with the electrolyte.…</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr"/>
+      <c r="H16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>只写缩写</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>P627 只写了「DOL」，按1,3-二氧戊环（1,3-dioxolane）处理，可以吗？</t>
+          <t>P627</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>领域通用含义；另有 26 篇写了全称（P034、P038、P054、P062、P102、P113、P137、P141、P156、P160、P169、P215、P218、P307、P309、P315、P323、P334、P380、P425、P510、P536、P558、P609、P633、P668），结构与 PubChem 一致</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr"/>
+          <t>DOL</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>P627</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="n"/>
+          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>[M0074] …Two cells of each polysulfide were prepared, one containing conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v)) and another containing LP30 in order to analyze the interaction of polysulfide with the electrolyte.…</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr"/>
+      <c r="H17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>合写拆分</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>下面这些写法把两种溶剂合写成一条，已拆成两个组分分别记录，可以吗？</t>
+          <t>P627</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>P156「DME/DOL」→ DME＋DOL；P307「DOL/DME（冲突）」→ DOL＋DME；P633「DEE/DME」→ DEE＋DME；P633「DOL/DME」→ DOL＋DME</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr"/>
+          <t>LiTFSI</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>P156、P307、P633</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="n"/>
+          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>[M0074] …Two cells of each polysulfide were prepared, one containing conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v)) and another containing LP30 in order to analyze the interaction of polysulfide with the electrolyte.…</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr"/>
+      <c r="H18" s="1" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>仅认身份</t>
+          <t>写法</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>多硫化锂和单列离子（Li2S、Li2S2、Li2S3、Li2S4、Li2S5、Li2S6、Li2S7、Li2S8、LiPS_x、ION_Li、ION_NO3、ION_PF6、ION_Br、ION_TMA、ION_FSI、ION_TFSI）只用来认身份、不算描述符，结构按化学式写。一般不用看</t>
+          <t>P633</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>B 档</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr"/>
-      <c r="E19" s="1" t="inlineStr"/>
-      <c r="F19" s="1" t="n"/>
+          <t>LiFSI</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>本篇原文未找到全称；原文 M0047 全称写作“lithium bis(fluoromethanesulfonyl)imide (LiFSI; anhydrous, 98%, TCI)”，多了 methane（那是另一种结构）；缩写、TCI 商品和 M0190 的 FSI⁻ 都指双氟磺酰亚胺锂</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>[M0047] …Electrolyte preparati on The electrolyte was prepared by dissolving 1.0 M lithium bis(f luoromethanesulfonyl)imide (LiFSI; anhydrous, 98%, TCI) and 0.2 M lithium nitrate (LiNO3; anhydrous, 99%, Alfa Aesar) in selected solvents.…
+[M0190] …Upon dissolution of LiFSI, the coordination between Li+ cations and FSI- anions decreases, accompanied by enhanced Li+ -solvent interactions.…</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr"/>
+      <c r="H19" s="1" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>写法</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>P156、P307、P633</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>合写的溶剂</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>提取把两种溶剂写成一条，身份没有疑问，已拆成两个组分：P156「DME/DOL」→ DME＋DOL；P307「DOL/DME（冲突）」→ DOL＋DME；P633「DEE/DME」→ DEE＋DME；P633「DOL/DME」→ DOL＋DME</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr"/>
+      <c r="H20" s="1" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>组分</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>多硫化锂与单列离子</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>B 档只认身份、不算描述符，结构按化学式写：Li2S、Li2S2、Li2S3、Li2S4、Li2S5、Li2S6、Li2S7、Li2S8、LiPS_x、ION_Li、ION_NO3、ION_PF6、ION_Br、ION_TMA、ION_FSI、ION_TFSI</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr"/>
+      <c r="G21" s="1" t="inlineStr"/>
+      <c r="H21" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2252,7 +2503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2263,7 +2514,6 @@
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2307,11 +2557,6 @@
           <t>论文</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>不对就写✍</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="155" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -2337,7 +2582,7 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>P034 [M0046] …mposed of 0.1 M LiNO3 additive and 1 M lithium bis(trifluoromethanesulfonyl) imide (LiTFSI) in 1,2- dimethoxyethane (DME) and 1,3-dioxolane (DOL) (v/v, 1:1).…</t>
+          <t>P034 [M0046] …as composed of 0.1 M LiNO3 additive and 1 M lithium bis(trifluoromethanesulfonyl) imide (LiTFSI) in 1,2- dimethoxyethane (DME) and 1,3-dioxolane (DOL) (v/v, 1:1).…</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -2350,7 +2595,6 @@
           <t>P034、P038、P054、P062、P102、P113、P137、P141、P156、P160、P169、P215、P218、P307、P309、P315、P323、P334、P380、P386、P425、P451、P510、P536、P558、P609、P627、P633、P668</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr"/>
     </row>
     <row r="3" ht="155" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -2389,7 +2633,6 @@
           <t>P034、P038、P054、P062、P102、P113、P137、P141、P156、P160、P169、P215、P218、P307、P309、P315、P323、P334、P380、P425、P510、P536、P558、P609、P627、P633、P668</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr"/>
     </row>
     <row r="4" ht="155" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -2428,7 +2671,6 @@
           <t>P137、P380、P536、P633</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5" ht="155" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -2467,7 +2709,6 @@
           <t>P215、P633</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr"/>
     </row>
     <row r="6" ht="155" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -2506,7 +2747,6 @@
           <t>P215</t>
         </is>
       </c>
-      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7" ht="155" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -2545,7 +2785,6 @@
           <t>P451</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8" ht="155" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -2584,7 +2823,6 @@
           <t>P451</t>
         </is>
       </c>
-      <c r="I8" s="1" t="inlineStr"/>
     </row>
     <row r="9" ht="155" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
@@ -2623,7 +2861,6 @@
           <t>P315、P323</t>
         </is>
       </c>
-      <c r="I9" s="1" t="inlineStr"/>
     </row>
     <row r="10" ht="155" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
@@ -2662,7 +2899,6 @@
           <t>P633</t>
         </is>
       </c>
-      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11" ht="155" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
@@ -2701,7 +2937,6 @@
           <t>P425、P451、P558</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr"/>
     </row>
     <row r="12" ht="155" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
@@ -2732,7 +2967,7 @@
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>PubChem 未收录</t>
+          <t>PubChem 未收录；原文结构核对一致</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
@@ -2740,7 +2975,6 @@
           <t>P386</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr"/>
     </row>
     <row r="13" ht="155" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
@@ -2779,7 +3013,6 @@
           <t>P386</t>
         </is>
       </c>
-      <c r="I13" s="1" t="inlineStr"/>
     </row>
     <row r="14" ht="155" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
@@ -2818,7 +3051,6 @@
           <t>P215</t>
         </is>
       </c>
-      <c r="I14" s="1" t="inlineStr"/>
     </row>
     <row r="15" ht="155" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -2857,7 +3089,6 @@
           <t>P102、P315、P451、P594、P627</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr"/>
     </row>
     <row r="16" ht="155" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
@@ -2896,7 +3127,6 @@
           <t>P102、P160</t>
         </is>
       </c>
-      <c r="I16" s="1" t="inlineStr"/>
     </row>
     <row r="17" ht="155" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
@@ -2935,7 +3165,6 @@
           <t>P160、P594</t>
         </is>
       </c>
-      <c r="I17" s="1" t="inlineStr"/>
     </row>
     <row r="18" ht="155" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
@@ -2974,7 +3203,6 @@
           <t>P102、P315、P451、P627</t>
         </is>
       </c>
-      <c r="I18" s="1" t="inlineStr"/>
     </row>
     <row r="19" ht="155" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
@@ -3009,7 +3237,6 @@
           <t>P594</t>
         </is>
       </c>
-      <c r="I19" s="1" t="inlineStr"/>
     </row>
     <row r="20" ht="155" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
@@ -3048,7 +3275,6 @@
           <t>P034、P062</t>
         </is>
       </c>
-      <c r="I20" s="1" t="inlineStr"/>
     </row>
     <row r="21" ht="155" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
@@ -3087,7 +3313,6 @@
           <t>P034、P062、P156</t>
         </is>
       </c>
-      <c r="I21" s="1" t="inlineStr"/>
     </row>
     <row r="22" ht="155" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
@@ -3126,7 +3351,6 @@
           <t>P510</t>
         </is>
       </c>
-      <c r="I22" s="1" t="inlineStr"/>
     </row>
     <row r="23" ht="155" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
@@ -3165,7 +3389,6 @@
           <t>P510</t>
         </is>
       </c>
-      <c r="I23" s="1" t="inlineStr"/>
     </row>
     <row r="24" ht="155" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
@@ -3204,7 +3427,6 @@
           <t>P510</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr"/>
     </row>
     <row r="25" ht="155" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
@@ -3243,7 +3465,6 @@
           <t>P034、P038、P054、P062、P113、P137、P141、P156、P160、P169、P218、P307、P315、P323、P334、P380、P425、P510、P536、P558、P609、P627、P668</t>
         </is>
       </c>
-      <c r="I25" s="1" t="inlineStr"/>
     </row>
     <row r="26" ht="155" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
@@ -3282,7 +3503,6 @@
           <t>P215、P309、P386、P425、P451、P609、P633</t>
         </is>
       </c>
-      <c r="I26" s="1" t="inlineStr"/>
     </row>
     <row r="27" ht="155" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
@@ -3321,7 +3541,6 @@
           <t>P034、P038、P054、P062、P113、P137、P141、P156、P169、P215、P218、P307、P309、P315、P323、P334、P380、P425、P536、P558、P609、P633、P668</t>
         </is>
       </c>
-      <c r="I27" s="1" t="inlineStr"/>
     </row>
     <row r="28" ht="155" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
@@ -3360,7 +3579,6 @@
           <t>P102、P315、P425、P451、P594、P627</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr"/>
     </row>
     <row r="29" ht="155" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
@@ -3399,7 +3617,6 @@
           <t>P425</t>
         </is>
       </c>
-      <c r="I29" s="1" t="inlineStr"/>
     </row>
     <row r="30" ht="155" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
@@ -3438,7 +3655,6 @@
           <t>P102</t>
         </is>
       </c>
-      <c r="I30" s="1" t="inlineStr"/>
     </row>
     <row r="31" ht="155" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
@@ -3477,7 +3693,6 @@
           <t>P160</t>
         </is>
       </c>
-      <c r="I31" s="1" t="inlineStr"/>
     </row>
     <row r="32" ht="155" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
@@ -3516,7 +3731,6 @@
           <t>P141</t>
         </is>
       </c>
-      <c r="I32" s="1" t="inlineStr"/>
     </row>
     <row r="33" ht="155" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
@@ -3555,7 +3769,6 @@
           <t>P038</t>
         </is>
       </c>
-      <c r="I33" s="1" t="inlineStr"/>
     </row>
     <row r="34" ht="155" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
@@ -3586,7 +3799,7 @@
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>未查询（按化学式书写）</t>
+          <t>未查询（按化学式书写）；原文结构核对一致</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
@@ -3594,7 +3807,6 @@
           <t>P038</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr"/>
     </row>
     <row r="35" ht="155" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
@@ -3633,7 +3845,6 @@
           <t>P307</t>
         </is>
       </c>
-      <c r="I35" s="1" t="inlineStr"/>
     </row>
     <row r="36" ht="155" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
@@ -3672,7 +3883,6 @@
           <t>P038</t>
         </is>
       </c>
-      <c r="I36" s="1" t="inlineStr"/>
     </row>
     <row r="37" ht="155" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
@@ -3711,7 +3921,6 @@
           <t>P334</t>
         </is>
       </c>
-      <c r="I37" s="1" t="inlineStr"/>
     </row>
     <row r="38" ht="155" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
@@ -3750,7 +3959,6 @@
           <t>P594</t>
         </is>
       </c>
-      <c r="I38" s="1" t="inlineStr"/>
     </row>
     <row r="39" ht="155" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
@@ -3789,7 +3997,6 @@
           <t>P536</t>
         </is>
       </c>
-      <c r="I39" s="1" t="inlineStr"/>
     </row>
     <row r="40" ht="155" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
@@ -3828,7 +4035,6 @@
           <t>P536</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr"/>
     </row>
     <row r="41" ht="155" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
@@ -3867,7 +4073,6 @@
           <t>P218</t>
         </is>
       </c>
-      <c r="I41" s="1" t="inlineStr"/>
     </row>
     <row r="42" ht="155" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
@@ -3906,7 +4111,6 @@
           <t>P558</t>
         </is>
       </c>
-      <c r="I42" s="1" t="inlineStr"/>
     </row>
     <row r="43" ht="155" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
@@ -3945,7 +4149,6 @@
           <t>P558</t>
         </is>
       </c>
-      <c r="I43" s="1" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -3966,7 +4169,7 @@
       <c r="D44" s="1" t="inlineStr"/>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>无 SMILES，见待你判断</t>
+          <t>无 SMILES，见读原文判定</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
@@ -3984,7 +4187,6 @@
           <t>P380</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4970,7 +5172,7 @@
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>PubChem 未收录</t>
+          <t>PubChem 未收录；原文结构核对一致</t>
         </is>
       </c>
       <c r="L12" s="1" t="n">
@@ -4991,14 +5193,10 @@
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t>🔶 PubChem 按全称未收录，结构以原文为准；🔶 自合成，按原文化学名（P386 M0052）绘制，待确认</t>
-        </is>
-      </c>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t>自合成，按原文化学名（P386 M0052）绘制，待确认</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -5051,7 +5249,7 @@
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>一致（CID 134171504）</t>
+          <t>一致（CID 134171504）；原文结构核对一致</t>
         </is>
       </c>
       <c r="L13" s="1" t="n">
@@ -5072,14 +5270,10 @@
       </c>
       <c r="P13" s="1" t="inlineStr">
         <is>
-          <t>🔶 自合成，按原文化学名（P386 M0052）绘制，待确认</t>
-        </is>
-      </c>
-      <c r="Q13" s="1" t="inlineStr">
-        <is>
-          <t>自合成，按原文化学名（P386 M0052）绘制，待确认</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -6676,7 +6870,7 @@
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>未查询（按化学式书写）</t>
+          <t>未查询（按化学式书写）；原文结构核对一致</t>
         </is>
       </c>
       <c r="L34" s="1" t="n">
@@ -6697,12 +6891,12 @@
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
-          <t>🔶 未用公共库核对，按化学式书写；🔶 按化学式书写；P038 化学氧化测试液中按 2.5 mM 加入</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
-          <t>按化学式书写；P038 化学氧化测试液中按 2.5 mM 加入</t>
+          <t>P038 化学氧化测试液中按 2.5 mM 加入</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7651,12 @@
       </c>
       <c r="P44" s="1" t="inlineStr">
         <is>
-          <t>🔶 金属配合物，在电解液中原位生成；原文 P380 M0031：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成。没有可靠的单一 SMILES，按前驱体记录身份，不算描述符</t>
+          <t>🔶 金属配合物，没有可靠的单一 SMILES，不算 RDKit 描述符，分析时按“含 Cu-2-T”分块记录。原文 P380：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成（M0031），为双 Cl 桥连的双核 Cu 配合物（M0042）；与 KPF₆ 交换得 Cu-2-PF₆，再溶入 1 M LiTFSI＋2 wt% LiNO₃ 的 DME/DOL 中由 TFSI⁻ 置换得 Cu-2-T（M0040），为单 Cl 桥连的双核 Cu 配合物（M0043，Figure 1a 晶体结构，CCDC 2243502）</t>
         </is>
       </c>
       <c r="Q44" s="1" t="inlineStr">
         <is>
-          <t>金属配合物，在电解液中原位生成；原文 P380 M0031：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成。没有可靠的单一 SMILES，按前驱体记录身份，不算描述符</t>
+          <t>金属配合物，没有可靠的单一 SMILES，不算 RDKit 描述符，分析时按“含 Cu-2-T”分块记录。原文 P380：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成（M0031），为双 Cl 桥连的双核 Cu 配合物（M0042）；与 KPF₆ 交换得 Cu-2-PF₆，再溶入 1 M LiTFSI＋2 wt% LiNO₃ 的 DME/DOL 中由 TFSI⁻ 置换得 Cu-2-T（M0040），为单 Cl 桥连的双核 Cu 配合物（M0043，Figure 1a 晶体结构，CCDC 2243502）</t>
         </is>
       </c>
     </row>
@@ -8931,7 +9125,7 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>DME：[M0046] …mposed of 0.1 M LiNO3 additive and 1 M lithium bis(trifluoromethanesulfonyl) imide (LiTFSI) in 1,2- dimethoxyethane (DME) and 1,3-dioxolane (DOL) (v/v, 1:1). …</t>
+          <t>DME：[M0046] …as composed of 0.1 M LiNO3 additive and 1 M lithium bis(trifluoromethanesulfonyl) imide (LiTFSI) in 1,2- dimethoxyethane (DME) and 1,3-dioxolane (DOL) (v/v, 1:1). …</t>
         </is>
       </c>
     </row>
@@ -8976,7 +9170,7 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称，按常用含义</t>
+          <t>本篇原文未找到全称；全文只写缩写；M0060 与 dimethyl tetrasulfide (DMTtS)、DMDS 并列为二甲基多硫醚中间体，S0005 把 DMTS 加入电解液测 ¹H NMR，判为二甲基三硫醚</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
@@ -9297,13 +9491,17 @@
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr"/>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>本篇原文未找到全称；原文 M0214 全称写作“1,2-dioxolane (DOL)”，位次有误：1,2-二氧戊环是另一种异构体（环状过氧化物），不作电解液溶剂；本篇其余各处都是“1 M LiTFSI in DOL/DME with 1 wt% LiNO3”标准醚类电解液（M0060、M0079、S0014），判为 1,3-二氧戊环</t>
+        </is>
+      </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>DOL：[M0214] …The electrolyte containing 1 M bis(trifluoromethane) sulfonamide lithium (LiTFSI)/1,2-dioxolane (DOL): dimethoxyethane (DME) (1:1 by volume) with 1 wt% LiNO3 and 150 mM LiI or 50 mM InI3 additive…</t>
+          <t>DOL：本篇未找到全称</t>
         </is>
       </c>
     </row>
@@ -9619,17 +9817,13 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>本篇原文未找到全称，按常用含义</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>LiTFSI：本篇未找到全称</t>
+          <t>LiTFSI：[M0214] …The electrolyte containing 1 M bis(trifluoromethane) sulfonamide lithium (LiTFSI)/1,2-dioxolane (DOL): dimethoxyethane (DME) (1:1 by volume) with 1 wt% LiNO3…</t>
         </is>
       </c>
     </row>
@@ -10819,12 +11013,12 @@
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>TFSA 与 TFSI 是同一阴离子的两种缩写</t>
+          <t>TFSA 与 TFSI 是同一阴离子的两种缩写；P137 M0014 写明 Li-bis(trifluoromethane sulfonyl)amide (Li[TFSA])</t>
         </is>
       </c>
       <c r="J44" s="1" t="inlineStr">
@@ -11191,17 +11385,13 @@
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>本篇原文未找到全称，按常用含义</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>LiTFSI：本篇未找到全称</t>
+          <t>LiTFSI：[M0247] …Experimental Section Electrolyte Characterization: Electrolytes with varying ratios of lithium bis(trifluoromethanesulphonyl)imide (LiTFSI, 3M) and lithium nitrate (LiNO3, Sigma-Aldrich) salts were prepared, totaling a L…</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11763,7 @@
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称，按常用含义；原文 M0024 写作“1,2-dimethoxymethane (DME)”，名称有误，按 1,2-二甲氧基乙烷处理</t>
+          <t>本篇原文未找到全称；原文 M0024 写“1,2-dimethoxymethane (DME)”，这个名称不成立（甲烷只有一个碳，不会有 1,2 位）；M0025 写 DME 沸点 42 °C，这是二甲氧基甲烷（甲缩醛）的沸点，1,2-二甲氧基乙烷为 85 °C。但对照电解液是锂硫标准的“1 M LiTFSI/DOL+DME（1:1）”（S0008），M0048 引用的 Suo 等 7 M LiTFSI-DOL:DME 也是 1,2-二甲氧基乙烷，判为 1,2-二甲氧基乙烷</t>
         </is>
       </c>
       <c r="J60" s="1" t="inlineStr">
@@ -11756,17 +11946,13 @@
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>本篇原文未找到全称，按常用含义</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr">
         <is>
-          <t>LiTFSI：本篇未找到全称</t>
+          <t>LiTFSI：[M0003] …Herein, we demonstrated a novel kind of flame-retardant concentrated electrolyte (6.5 M lithium bis(trifluoromethylsulphonyl)imide/fluoroethylene carbonate) for highly-safe and widetemperature lithium-sulfur batteries. …</t>
         </is>
       </c>
     </row>
@@ -11852,12 +12038,12 @@
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>本篇 DIOX 指 1,3-二氧戊环（M0009），不是 1,4-二氧六环</t>
+          <t>M0009 写明 1,3-dioxolane (DIOX)；DIOX 常指 1,4-二氧六环，本篇不是</t>
         </is>
       </c>
       <c r="J66" s="1" t="inlineStr">
@@ -13288,7 +13474,7 @@
       <c r="I97" s="1" t="inlineStr"/>
       <c r="J97" s="1" t="inlineStr">
         <is>
-          <t>DME：[M0030] … (KHFDF) salt and bistrifluoromethanesulfonimide lithium salt in the liquid 1,3-dioxlane (DOL)/1,2- dimethoxyethane (DME) solvents to enable the longest cycle life of Li‒S pouch cell passing 200 cycles. …</t>
+          <t>DME：[M0030] …ssium (KHFDF) salt and bistrifluoromethanesulfonimide lithium salt in the liquid 1,3-dioxlane (DOL)/1,2- dimethoxyethane (DME) solvents to enable the longest cycle life of Li‒S pouch cell passing 200 cycles. …</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13571,7 @@
       <c r="J99" s="1" t="inlineStr">
         <is>
           <t>DOL：[M0030] … disulfonimide potassium (KHFDF) salt and bistrifluoromethanesulfonimide lithium salt in the liquid 1,3-dioxlane (DOL)/1,2- dimethoxyethane (DME) solvents to enable the longest cycle life of Li‒S pouch cell passi…
-DME：[M0030] … (KHFDF) salt and bistrifluoromethanesulfonimide lithium salt in the liquid 1,3-dioxlane (DOL)/1,2- dimethoxyethane (DME) solvents to enable the longest cycle life of Li‒S pouch cell passing 200 cycles. …</t>
+DME：[M0030] …ssium (KHFDF) salt and bistrifluoromethanesulfonimide lithium salt in the liquid 1,3-dioxlane (DOL)/1,2- dimethoxyethane (DME) solvents to enable the longest cycle life of Li‒S pouch cell passing 200 cycles. …</t>
         </is>
       </c>
     </row>
@@ -13615,7 +13801,7 @@
       <c r="I104" s="1" t="inlineStr"/>
       <c r="J104" s="1" t="inlineStr">
         <is>
-          <t>DOL：[M0025] …adopts low-freezing-point ether solvents, of which the commonly used dimethoxyethane (DME) and 1,3- dioxolane (DOL) have melting points as low as -58 and -95 °C respectively,[3] allowing relatively high ionic …</t>
+          <t>DOL：[M0025] …LSB) adopts low-freezing-point ether solvents, of which the commonly used dimethoxyethane (DME) and 1,3- dioxolane (DOL) have melting points as low as -58 and -95 °C respectively,[3] allowing relatively high ionic …</t>
         </is>
       </c>
     </row>
@@ -13983,7 +14169,7 @@
       <c r="I112" s="1" t="inlineStr"/>
       <c r="J112" s="1" t="inlineStr">
         <is>
-          <t>DME：[M0053] …nsity of 0.776 gcm  3.[37] Polysulfide solubility can be adjusted by adding limited amounts of 1,2- dimethoxyethane (DME) or 1,3-dioxolane (DOL) to the HME- based electrolytes to improve the kinetics of the Li  S ba…</t>
+          <t>DME：[M0053] …ow density of 0.776 gcm  3.[37] Polysulfide solubility can be adjusted by adding limited amounts of 1,2- dimethoxyethane (DME) or 1,3-dioxolane (DOL) to the HME- based electrolytes to improve the kinetics of the Li  S ba…</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14261,7 @@
       <c r="I114" s="1" t="inlineStr"/>
       <c r="J114" s="1" t="inlineStr">
         <is>
-          <t>DME：[M0053] …nsity of 0.776 gcm  3.[37] Polysulfide solubility can be adjusted by adding limited amounts of 1,2- dimethoxyethane (DME) or 1,3-dioxolane (DOL) to the HME- based electrolytes to improve the kinetics of the Li  S ba…</t>
+          <t>DME：[M0053] …ow density of 0.776 gcm  3.[37] Polysulfide solubility can be adjusted by adding limited amounts of 1,2- dimethoxyethane (DME) or 1,3-dioxolane (DOL) to the HME- based electrolytes to improve the kinetics of the Li  S ba…</t>
         </is>
       </c>
     </row>
@@ -14764,7 +14950,7 @@
       </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称，按常用含义；原文 M0169 写作“1, 2-dimethoxythane (DME)”，拼写有误，按 1,2-二甲氧基乙烷处理</t>
+          <t>本篇原文未找到全称；原文 M0169 写“1, 2-dimethoxythane (DME, Aladdin, 99.5 %)”，少一个 e，判为 1,2-二甲氧基乙烷</t>
         </is>
       </c>
       <c r="J129" s="1" t="inlineStr">
@@ -14815,7 +15001,7 @@
       <c r="I130" s="1" t="inlineStr"/>
       <c r="J130" s="1" t="inlineStr">
         <is>
-          <t>DOL：[M0169] …3 (Aladdin, 99.9 %) in the mixture solvent with 1, 2-dimethoxythane (DME, Aladdin, 99.5 %) and 1, 3-dioxolane (DOL, Aladdin, 99.5 %) (v/ Fig. 5. …</t>
+          <t>DOL：[M0169] … LiNO3 (Aladdin, 99.9 %) in the mixture solvent with 1, 2-dimethoxythane (DME, Aladdin, 99.5 %) and 1, 3-dioxolane (DOL, Aladdin, 99.5 %) (v/ Fig. 5. …</t>
         </is>
       </c>
     </row>
@@ -15085,17 +15271,13 @@
       </c>
       <c r="H136" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I136" s="1" t="inlineStr">
-        <is>
-          <t>本篇原文未找到全称，按常用含义</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I136" s="1" t="inlineStr"/>
       <c r="J136" s="1" t="inlineStr">
         <is>
-          <t>LiTFSI：本篇未找到全称</t>
+          <t>LiTFSI：[M0169] …Preparation of electrolytes The base electrolyte is 1 M lithium bis(trifluoromethanesulf ony)imide (LiTFSI, Aladdin, 99.9 %) and 2 wt% LiNO3 (Aladdin, 99.9 %) in the mixture solvent with 1…</t>
         </is>
       </c>
     </row>
@@ -15503,17 +15685,13 @@
       </c>
       <c r="H145" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I145" s="1" t="inlineStr">
-        <is>
-          <t>本篇原文未找到全称，按常用含义</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I145" s="1" t="inlineStr"/>
       <c r="J145" s="1" t="inlineStr">
         <is>
-          <t>LiTFSI：本篇未找到全称</t>
+          <t>LiTFSI：[M0054] …version based on Cu-2-T and G. symmetric and asymmetric stretching vibrations of S─N bonds in TFSI-(bis(trifluoromethane sulfonimide) anion),[34] and disappeared peak signal at 555 cm-1, substantiating the successful anion re…</t>
         </is>
       </c>
     </row>
@@ -15553,17 +15731,13 @@
       </c>
       <c r="H146" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I146" s="1" t="inlineStr">
-        <is>
-          <t>本篇原文未找到全称，按常用含义</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I146" s="1" t="inlineStr"/>
       <c r="J146" s="1" t="inlineStr">
         <is>
-          <t>LiTFSI：本篇未找到全称</t>
+          <t>LiTFSI：[M0054] …version based on Cu-2-T and G. symmetric and asymmetric stretching vibrations of S─N bonds in TFSI-(bis(trifluoromethane sulfonimide) anion),[34] and disappeared peak signal at 555 cm-1, substantiating the successful anion re…</t>
         </is>
       </c>
     </row>
@@ -15603,12 +15777,12 @@
       </c>
       <c r="H147" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>原文未报告反离子</t>
+          <t>P380 中 PF₆⁻ 来自 KPF₆ 阴离子交换得到的 Cu-2-PF₆（M0033、M0040），平衡离子是 Cu-2 配合物阳离子，溶入电解液后被 TFSI⁻ 置换</t>
         </is>
       </c>
       <c r="J147" s="1" t="inlineStr">
@@ -15796,7 +15970,7 @@
       </c>
       <c r="I151" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称，按常用含义</t>
+          <t>本篇原文未找到全称；全文只写缩写；S0029 写 LiFSI 购自 Tansoole，M0174 写富 LiF 主要来自 LiFSI 盐，按双氟磺酰亚胺锂</t>
         </is>
       </c>
       <c r="J151" s="1" t="inlineStr">
@@ -16951,7 +17125,7 @@
       <c r="I176" s="1" t="inlineStr"/>
       <c r="J176" s="1" t="inlineStr">
         <is>
-          <t>DME：[S0014] …thium bis(trifluoro-sulfonyl)imide, LiFSI= lithium bis(fluoro-sulfonyl)imide, DOL=1,3 dioxane, DME= dimethoxyethane, PC = propylene carbonate, EC = ethylene carbonate, DEC = diethylene carbonate, TEGDME= tetraethyle…</t>
+          <t>DME：[M0005] … the conventional electrolyte solution, which is 1 M LiTFSI salt in a 50/50 vol% mixture of DOL and dimethoxy ethane (DME), the LiTFSI electrolyte with DOL/hydrocarbon solvents demonstrate better cycling stability, c…</t>
         </is>
       </c>
     </row>
@@ -17548,7 +17722,7 @@
       </c>
       <c r="I189" s="1" t="inlineStr">
         <is>
-          <t>同一液体原文两种写法：M0206 写 tetraglyme，S0018 写 tetracarboxylic ester；按 tetraglyme 处理，待确认</t>
+          <t>主文 M0206 图注写 Li||Li2S8/tetraglyme；SI S0018 同一实验写“tetracarboxylic ester”，这不是常用电解液溶剂的名称，判为 SI 笔误，按四乙二醇二甲醚</t>
         </is>
       </c>
       <c r="J189" s="1" t="inlineStr">
@@ -17823,17 +17997,13 @@
       </c>
       <c r="H195" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I195" s="1" t="inlineStr">
-        <is>
-          <t>本篇原文未找到全称，按常用含义</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I195" s="1" t="inlineStr"/>
       <c r="J195" s="1" t="inlineStr">
         <is>
-          <t>LiTFSI：本篇未找到全称</t>
+          <t>LiTFSI：[M0026] …E-based EPSE is chosen as the baseline electrolyte.31 The baseline electrolyte consists of 1.0 M Li bis(trifluoromethanesulfonyl)- imide (LiTFSI) and 2.0 wt % LiNO3 dissolved in a solution of TTE/dimethoxyethane (DME)/1,3-di…</t>
         </is>
       </c>
     </row>
@@ -18016,7 +18186,7 @@
       </c>
       <c r="I199" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称，按常用含义</t>
+          <t>本篇原文未找到全称；全文只写缩写；M0031 写常规碳酸酯电解液，M0069 中 DEC 与 EC、PF₆⁻ 并列，判为碳酸二乙酯</t>
         </is>
       </c>
       <c r="J199" s="1" t="inlineStr">
@@ -18389,7 +18559,7 @@
       <c r="I207" s="1" t="inlineStr"/>
       <c r="J207" s="1" t="inlineStr">
         <is>
-          <t>DME：[M0047] … a conventional com - mercial electrolyte (1 M LiTFSI and 0.1 M LiNO 3 in a 1:1 v/v mixture of 1,2- dimethoxyethane (DME) and DOL). …</t>
+          <t>DME：[M0047] …ified a conventional com - mercial electrolyte (1 M LiTFSI and 0.1 M LiNO 3 in a 1:1 v/v mixture of 1,2- dimethoxyethane (DME) and DOL). …</t>
         </is>
       </c>
     </row>
@@ -18435,7 +18605,7 @@
       <c r="I208" s="1" t="inlineStr"/>
       <c r="J208" s="1" t="inlineStr">
         <is>
-          <t>DOL：[M0030] …ap arises from a fundamental incompatibility: LiFSI is known to initiate the polymerization of 1,3- dioxolane (DOL), a common cosolvent in Li- S electrolytes, leading to the formation of poly(DOL) [ 25]. …</t>
+          <t>DOL：[M0030] …ble gap arises from a fundamental incompatibility: LiFSI is known to initiate the polymerization of 1,3- dioxolane (DOL), a common cosolvent in Li- S electrolytes, leading to the formation of poly(DOL) [ 25]. …</t>
         </is>
       </c>
     </row>
@@ -18756,7 +18926,7 @@
       </c>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称，按常用含义</t>
+          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
         </is>
       </c>
       <c r="J215" s="1" t="inlineStr">
@@ -18806,7 +18976,7 @@
       </c>
       <c r="I216" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称，按常用含义</t>
+          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
         </is>
       </c>
       <c r="J216" s="1" t="inlineStr">
@@ -18948,7 +19118,7 @@
       </c>
       <c r="I219" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称，按常用含义</t>
+          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
         </is>
       </c>
       <c r="J219" s="1" t="inlineStr">
@@ -19468,7 +19638,7 @@
       </c>
       <c r="I230" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称，按常用含义</t>
+          <t>本篇原文未找到全称；原文 M0047 全称写作“lithium bis(fluoromethanesulfonyl)imide (LiFSI; anhydrous, 98%, TCI)”，多了 methane（那是另一种结构）；缩写、TCI 商品和 M0190 的 FSI⁻ 都指双氟磺酰亚胺锂</t>
         </is>
       </c>
       <c r="J230" s="1" t="inlineStr">

--- a/output/组分结构表_F版30篇_2026-10-31/组分结构表.xlsx
+++ b/output/组分结构表_F版30篇_2026-10-31/组分结构表.xlsx
@@ -1198,6 +1198,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1490,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1537,12 +1562,12 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>20 行：原文只有缩写、名称写错、自合成、没有公共库记录等情况，Claude 读原文（含 PDF 里的结构图）后的判定，附原句。“剩余疑点”列非空的 3 行是原文自身矛盾或信息不全</t>
+          <t>20 行：原文只有缩写、名称写错、自合成、没有公共库记录等情况，Claude 读原文（含 PDF 里的结构图）后的判定，附原句。“剩余疑点”列非空的 3 行是原文自身矛盾或信息不全；你写过意见的行，最后一列是 Claude 的回复</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>不用逐条确认；有不同意见再在最后一列写</t>
+          <t>不用逐条确认；有不同意见再在倒数第二列写</t>
         </is>
       </c>
     </row>
@@ -1663,71 +1688,79 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>✅ 的写法同时满足两条：本篇原文里找到了全称；用这个全称去 PubChem 查到的结构和我们写的一致（PubChem 没有的自合成分子，改用原文的结构图、合成路线和谱图核对）。🔶 是 Claude 读原文后判定的，依据见“读原文判定”页。</t>
+          <t>✅ 的写法满足其一：① 本篇原文里找到了全称，且用这个全称去 PubChem 查到的结构和我们写的一致（PubChem 没有的自合成分子，改用原文的结构图、合成路线和谱图核对）；② 本篇只有缩写（或全称写错），但这个缩写在本机 670 篇锂硫文献里是通用缩写（定义它的文献 ≥5 篇且 ≥90% 指同一物质，见缩写词典.json）——DME、DOL 这类常用组分按其他文献同一物质处理（用户 10-31 定）。🔶 是 Claude 读原文后判定的，依据见“读原文判定”页。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>原文没有结构图时怎么定结构：① 系统化学名本身就唯一确定结构（如 2,3-dimethylbutane），商品溶剂和盐大多靠这个；② CAS 号、供应商；③ 合成路线（原料＋反应推出产物，P386 的两个自合成醚就是这样核的，SI 的结构图只是再确认）；④ 核磁等谱图佐证；⑤ 只有缩写时，领域通用且语境一致（如“常规醚类电解液 1 M LiTFSI in DME:DOL”）按通用含义，标 🔶；缩写有歧义又没有全称时不猜，按“结构未公开”不收录。</t>
+          <t>为什么不用 PubChem 等公共库查缩写：公共库按缩写查会返回错误化合物（10-31 实测 DOL、TTE、CSA、DMA、DIPS 都错），ChemSpider、CAS Common Chemistry 等通用库同理，缩写在不同领域指不同物质（DME 在别的领域常指气体二甲醚）。电解液专门数据库（如 ComBat 56 种溶剂、CALiSol-23）只覆盖几十种常见溶剂、不含添加剂和介体，可作抽查对照。所以缩写用本领域文献自己的定义来判：缩写词典统计了 670 篇文献里“全称 (缩写)”的写法；DEE（15 篇乙醚、6 篇二乙氧基乙烷）这类有歧义的缩写，必须看本篇全称。公共库只用全称查。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>同分异构体：分子式一样、结构不同的分子，SMILES 和 InChIKey 都不同，不会被当成同一个。本批就有两对：正己烷与 2,3-二甲基丁烷（都是 C₆H₁₄），PPEO-CF₃ 与 PXEO-CF₃（正丙基与异丙基，都是 C₇H₁₃F₃O₂）。所以身份按结构定，不按化学式定；用哪个异构体看原文全称（如 P510 写明 “n-hexane”“2,3 dimethylbutane”）。</t>
+          <t>原文没有结构图时怎么定结构：① 系统化学名本身就唯一确定结构（如 2,3-dimethylbutane），商品溶剂和盐大多靠这个；② CAS 号、供应商；③ 合成路线（原料＋反应推出产物，P386 的两个自合成醚就是这样核的，SI 的结构图只是再确认）；④ 核磁等谱图佐证；⑤ 只有缩写时查缩写词典：通用缩写按通用含义记 ✅；缩写有歧义又没有全称时不猜，按“结构未公开”不收录。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>立体异构：PC、FEC 有一个手性碳，商品是两种构型各半的混合物，SMILES 不写构型标记，InChIKey 第二段为 UHFFFAOYSA（表示未指定立体）。以后原文若写明某一构型或顺/反式，再写构型标记，与混合物算不同组分。</t>
+          <t>同分异构体：分子式一样、结构不同的分子，SMILES 和 InChIKey 都不同，不会被当成同一个。本批就有两对：正己烷与 2,3-二甲基丁烷（都是 C₆H₁₄），PPEO-CF₃ 与 PXEO-CF₃（正丙基与异丙基，都是 C₇H₁₃F₃O₂）。所以身份按结构定，不按化学式定；用哪个异构体看原文全称（如 P510 写明 “n-hexane”“2,3 dimethylbutane”）。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>描述符怎么定的：分子量、原子数、环数、可旋转键数、TPSA、氢键受体数对任何分子都能算，以后不用改；官能团标签是按锂硫电解液常见类别预先定的，不是按这 30 篇定的（本批没有砜、P=O、腈，这几列都是 0）。全量提取出现新类别时加标签，只多一列，已有组分的其他数值不变。</t>
+          <t>立体异构：PC、FEC 有一个手性碳，商品是两种构型各半的混合物，SMILES 不写构型标记，InChIKey 第二段为 UHFFFAOYSA（表示未指定立体）。以后原文若写明某一构型或顺/反式，再写构型标记，与混合物算不同组分。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>覆盖检查：每次重跑都检查 A 档有没有组分一个标签都没命中（烃（没有极性官能团，这本身就是信息）和不含碳的无机盐/离子（组分身份本身就是特征）除外）。本次全部覆盖；10-31 这项检查查出 TFSI/FSI/OTf 等阴离子的磺酰基、苯乙胺/苄胺/季铵的氮没有标签，已补“磺酰基”“胺/铵氮”两列，另加 Cl/Br/I 原子数、芳环数。</t>
+          <t>描述符怎么定的：分子量、原子数、环数、可旋转键数、TPSA、氢键受体数对任何分子都能算，以后不用改；官能团标签是按锂硫电解液常见类别预先定的，不是按这 30 篇定的（本批没有砜、P=O、腈，这几列都是 0）。全量提取出现新类别时加标签，只多一列，已有组分的其他数值不变。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>描述符是结构特征，不等于配位强度、介电常数或溶解度。Morgan 指纹对小分子溶剂很粗：DME 与 DOL 同为醚，相似度却为 0，所以分类别看官能团标签，不看指纹。</t>
+          <t>覆盖检查：每次重跑都检查 A 档有没有组分一个标签都没命中（烃（没有极性官能团，这本身就是信息）和不含碳的无机盐/离子（组分身份本身就是特征）除外）。本次全部覆盖；10-31 这项检查查出 TFSI/FSI/OTf 等阴离子的磺酰基、苯乙胺/苄胺/季铵的氮没有标签，已补“磺酰基”“胺/铵氮”两列，另加 Cl/Br/I 原子数、芳环数。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>覆盖：组分条目 1257 条 → 对应到组分 1173 条，未收录（有原因）84 条，对不上 0 条。规则见方案 §5.8。</t>
+          <t>描述符是结构特征，不等于配位强度、介电常数或溶解度。Morgan 指纹对小分子溶剂很粗：DME 与 DOL 同为醚，相似度却为 0，所以分类别看官能团标签，不看指纹。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>覆盖：组分条目 1257 条 → 对应到组分 1173 条，未收录（有原因）84 条，对不上 0 条。规则见方案 §5.8。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>配方挂接与单位换算待 F 版 30 篇人工复核完成后进行；“顺带发现的提取问题_复核完再看.json”请在复核完成后再打开。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A21:C21"/>
@@ -1746,7 +1779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1756,7 +1789,8 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1800,6 +1834,11 @@
           <t>有不同意见再写✍</t>
         </is>
       </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Claude 回复</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1833,7 +1872,8 @@
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr"/>
+      <c r="I2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1867,7 +1907,8 @@
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr"/>
-      <c r="H3" s="1" t="n"/>
+      <c r="H3" s="1" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1901,7 +1942,8 @@
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr"/>
-      <c r="H4" s="1" t="n"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1926,20 +1968,29 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>没有单一结构，不算描述符</t>
+          <t>氧化还原介体（原文称均相催化剂）；整体没有单一 SMILES：金属 Cu、2 核、单 Cl 桥（Cu-2 前驱体为双 Cl 桥）、反离子 TFSI⁻（ION_TFSI） 记为类别特征，配体1,10-菲咯啉单独算描述符</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>金属配合物，没有可靠的单一 SMILES，不算 RDKit 描述符，分析时按“含 Cu-2-T”分块记录。原文 P380：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成（M0031），为双 Cl 桥连的双核 Cu 配合物（M0042）；与 KPF₆ 交换得 Cu-2-PF₆，再溶入 1 M LiTFSI＋2 wt% LiNO₃ 的 DME/DOL 中由 TFSI⁻ 置换得 Cu-2-T（M0040），为单 Cl 桥连的双核 Cu 配合物（M0043，Figure 1a 晶体结构，CCDC 2243502）</t>
+          <t>金属配合物，整体没有可靠的单一 SMILES，整体不算 RDKit 描述符，配体 1,10-菲咯啉单独算；分析时按“含 Cu-2-T”分块记录。原文 P380：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成（M0031），为双 Cl 桥连的双核 Cu 配合物（M0042）；与 KPF₆ 交换得 Cu-2-PF₆，再溶入 1 M LiTFSI＋2 wt% LiNO₃ 的 DME/DOL 中由 TFSI⁻ 置换得 Cu-2-T（M0040），为单 Cl 桥连的双核 Cu 配合物（M0043，Figure 1a 晶体结构，CCDC 2243502）</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>确切组成见 CCDC 晶体数据</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="n"/>
+          <t>确切组成见 CCDC 晶体数据；原文没有氧化还原电位数值</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>这种无机物，你想想如何处理，而且它应该是氧化还原介体？</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>同意按氧化还原介体归类：原文称“均相催化剂”，但 M0092 写明不含硫的电池 CV 有一对氧化还原峰，在硫反应电压窗口内有本征氧化还原活性，起的是介体作用，类别已改。它不是纯无机物，是 Cu(II) 与有机配体 1,10-菲咯啉的配合物，整体没有可靠的单一 SMILES。处理：拆成能算的部分——金属 Cu、价态、双核、单 Cl 桥、反离子 TFSI⁻ 记为类别特征；配体 1,10-菲咯啉单独算 RDKit 描述符（描述符页“配体”行，已与 PubChem 核对）。对介体来说比结构更直接的特征是氧化还原电位，P380 只在 Figure S11 给 CV 曲线、正文没有数值，建议列入待定由读图补。LiI、InI₃、LiBr 这类简单无机介体按离子写 SMILES 就能算，同样建议补氧化还原对与电位。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1959,12 +2010,12 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0060 与 dimethyl tetrasulfide (DMTtS)、DMDS 并列为二甲基多硫醚中间体，S0005 把 DMTS 加入电解液测 ¹H NMR，判为二甲基三硫醚</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 6 篇里 6 篇指此物（100%，见缩写词典）；全文只写缩写；M0060 与 dimethyl tetrasulfide (DMTtS)、DMDS 并列为二甲基多硫醚中间体，S0005 把 DMTS 加入电解液测 ¹H NMR，判为二甲基三硫醚</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -1974,7 +2025,8 @@
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr"/>
-      <c r="H6" s="1" t="n"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1994,12 +2046,12 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；原文 M0214 全称写作“1,2-dioxolane (DOL)”，位次有误：1,2-二氧戊环是另一种异构体（环状过氧化物），不作电解液溶剂；本篇其余各处都是“1 M LiTFSI in DOL/DME with 1 wt% LiNO3”标准醚类电解液（M0060、M0079、S0014），判为 1,3-二氧戊环</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 412 篇里 398 篇指此物（97%，见缩写词典）；原文 M0214 全称写作“1,2-dioxolane (DOL)”，位次有误：1,2-二氧戊环是另一种异构体（环状过氧化物），不作电解液溶剂；本篇其余各处都是“1 M LiTFSI in DOL/DME with 1 wt% LiNO3”标准醚类电解液（M0060、M0079、S0014），判为 1,3-二氧戊环</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -2010,7 +2062,8 @@
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="n"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2044,7 +2097,16 @@
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr"/>
-      <c r="H8" s="1" t="n"/>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>TFSA 与 TFSI 应该不是一种物质吧，TFSA不是说了Amide，感觉像是有氨基的基团，你再好好看看。</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>核过，是同一种物质。这里的 amide 不是有机化学的酰胺基/氨基，而是无机命名里“带负电的氮”（R₂N⁻，IUPAC 叫 azanide，和 LDA“二异丙基氨基锂”的 amide 同义）。TFSA⁻ 与 TFSI⁻ 都是 N(SO₂CF₃)₂⁻，组成 C₂F₆NO₄S₂⁻，一个 H 都没有，不存在氨基；imide/amide 是同一阴离子的两种叫法，日本课题组（P137 的 [Li(G4)][TFSA] 溶剂化离子液体）习惯写 TFSA。证据：PubChem 按“lithium bis(trifluoromethanesulfonyl)amide”查得 CID 3816071，InChIKey 与表中 LiTFSI 相同；本机文献里定义 Li[TFSA] 的 5 篇全部指这个盐。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2064,12 +2126,12 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；原文 M0024 写“1,2-dimethoxymethane (DME)”，这个名称不成立（甲烷只有一个碳，不会有 1,2 位）；M0025 写 DME 沸点 42 °C，这是二甲氧基甲烷（甲缩醛）的沸点，1,2-二甲氧基乙烷为 85 °C。但对照电解液是锂硫标准的“1 M LiTFSI/DOL+DME（1:1）”（S0008），M0048 引用的 Suo 等 7 M LiTFSI-DOL:DME 也是 1,2-二甲氧基乙烷，判为 1,2-二甲氧基乙烷</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 437 篇里 413 篇指此物（95%，见缩写词典）；原文 M0024 写“1,2-dimethoxymethane (DME)”，这个名称不成立（甲烷只有一个碳，不会有 1,2 位）；M0025 写 DME 沸点 42 °C，这是二甲氧基甲烷（甲缩醛）的沸点，1,2-二甲氧基乙烷为 85 °C。但对照电解液是锂硫标准的“1 M LiTFSI/DOL+DME（1:1）”（S0008），M0048 引用的 Suo 等 7 M LiTFSI-DOL:DME 也是 1,2-二甲氧基乙烷，判为 1,2-二甲氧基乙烷</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -2085,7 +2147,16 @@
           <t>原文名称和沸点都指向二甲氧基甲烷，只能按语境判定；要确证只能问作者</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n"/>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>像是DME/DOL这种非常常用的电解液，有的文献没有给出全称，你可以把它看作跟其它文献DME/DOL一样的物质，这种也通常作为对比样存在</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>同意，已按你定的规则改：DME、DOL 这类常用组分，原文没写全称或全称写错，按其他文献同一物质处理，记 ✅，原文写错处留在备注。本机 670 篇文献里定义 DME 的 437 篇中 413 篇（95%）指 1,2-二甲氧基乙烷；写成 dimethyl ether（23 篇）、dimethoxymethane（8 篇）的几乎都出现在标准 DOL/DME 电解液里，是作者写错，P160 就是其中之一。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2119,7 +2190,8 @@
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr"/>
-      <c r="H10" s="1" t="n"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2139,12 +2211,12 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；原文 M0169 写“1, 2-dimethoxythane (DME, Aladdin, 99.5 %)”，少一个 e，判为 1,2-二甲氧基乙烷</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 437 篇里 413 篇指此物（95%，见缩写词典）；原文 M0169 写“1, 2-dimethoxythane (DME, Aladdin, 99.5 %)”，少一个 e，判为 1,2-二甲氧基乙烷</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -2153,7 +2225,8 @@
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr"/>
-      <c r="H11" s="1" t="n"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2188,7 +2261,8 @@
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr"/>
-      <c r="H12" s="1" t="n"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2208,12 +2282,12 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；S0029 写 LiFSI 购自 Tansoole，M0174 写富 LiF 主要来自 LiFSI 盐，按双氟磺酰亚胺锂</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 100 篇里 99 篇指此物（99%，见缩写词典）；全文只写缩写；S0029 写 LiFSI 购自 Tansoole，M0174 写富 LiF 主要来自 LiFSI 盐，按双氟磺酰亚胺锂</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -2223,7 +2297,16 @@
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr"/>
-      <c r="H13" s="1" t="n"/>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>你想想，LIFSI相比常用的LITFSI，少了个T，我猜测是少了“tri”，也就是基团不是“三个”，你再确定确定。</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>你的推断对了一半：T 指 trifluoromethyl（三氟甲基 CF₃），不是单独的 tri。TFSI 是双（三氟甲磺酰）亚胺，两个 S 上各连一个 CF₃；FSI 是双（氟磺酰）亚胺，CF₃ 整个换成一个 F 直接连在 S 上，没有碳。表中结构 F–SO₂–N⁻–SO₂–F（组成 F₂NO₄S₂⁻）就是这个。P386 全文只写 LiFSI；本机文献里定义 LiFSI 的 100 篇中 99 篇指双氟磺酰亚胺锂，按通用缩写记 ✅。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2262,7 +2345,8 @@
           <t>SI 与主文写法不一致，以主文为准</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2282,12 +2366,12 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0031 写常规碳酸酯电解液，M0069 中 DEC 与 EC、PF₆⁻ 并列，判为碳酸二乙酯</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 23 篇里 22 篇指此物（96%，见缩写词典）；全文只写缩写；M0031 写常规碳酸酯电解液，M0069 中 DEC 与 EC、PF₆⁻ 并列，判为碳酸二乙酯</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -2297,7 +2381,8 @@
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr"/>
-      <c r="H15" s="1" t="n"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2317,12 +2402,12 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 437 篇里 413 篇指此物（95%，见缩写词典）；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
@@ -2331,7 +2416,8 @@
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr"/>
-      <c r="H16" s="1" t="n"/>
+      <c r="H16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2351,12 +2437,12 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 412 篇里 398 篇指此物（97%，见缩写词典）；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
@@ -2365,7 +2451,8 @@
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr"/>
-      <c r="H17" s="1" t="n"/>
+      <c r="H17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2385,12 +2472,12 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 341 篇里 339 篇指此物（99%，见缩写词典）；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
@@ -2399,7 +2486,8 @@
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr"/>
-      <c r="H18" s="1" t="n"/>
+      <c r="H18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -2419,12 +2507,12 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；原文 M0047 全称写作“lithium bis(fluoromethanesulfonyl)imide (LiFSI; anhydrous, 98%, TCI)”，多了 methane（那是另一种结构）；缩写、TCI 商品和 M0190 的 FSI⁻ 都指双氟磺酰亚胺锂</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 100 篇里 99 篇指此物（99%，见缩写词典）；原文 M0047 全称写作“lithium bis(fluoromethanesulfonyl)imide (LiFSI; anhydrous, 98%, TCI)”，多了 methane（那是另一种结构）；缩写、TCI 商品和 M0190 的 FSI⁻ 都指双氟磺酰亚胺锂</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -2434,7 +2522,8 @@
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr"/>
-      <c r="H19" s="1" t="n"/>
+      <c r="H19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2464,7 +2553,8 @@
       </c>
       <c r="F20" s="1" t="inlineStr"/>
       <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="n"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2490,7 +2580,8 @@
       </c>
       <c r="F21" s="1" t="inlineStr"/>
       <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="n"/>
+      <c r="H21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4150,7 +4241,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="155" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
           <t>CU2T</t>
@@ -4169,7 +4260,7 @@
       <c r="D44" s="1" t="inlineStr"/>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>无 SMILES，见读原文判定</t>
+          <t>金属配合物；图为配体（1,10-菲咯啉）：3 个环（含芳环）；无极性官能团；无 F</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
@@ -7616,7 +7707,7 @@
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>添加剂（均相催化剂/介体）</t>
+          <t>氧化还原介体（原文称均相催化剂）</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
@@ -7651,12 +7742,12 @@
       </c>
       <c r="P44" s="1" t="inlineStr">
         <is>
-          <t>🔶 金属配合物，没有可靠的单一 SMILES，不算 RDKit 描述符，分析时按“含 Cu-2-T”分块记录。原文 P380：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成（M0031），为双 Cl 桥连的双核 Cu 配合物（M0042）；与 KPF₆ 交换得 Cu-2-PF₆，再溶入 1 M LiTFSI＋2 wt% LiNO₃ 的 DME/DOL 中由 TFSI⁻ 置换得 Cu-2-T（M0040），为单 Cl 桥连的双核 Cu 配合物（M0043，Figure 1a 晶体结构，CCDC 2243502）</t>
+          <t>🔶 金属配合物，整体没有可靠的单一 SMILES，整体不算 RDKit 描述符，配体 1,10-菲咯啉单独算；分析时按“含 Cu-2-T”分块记录。原文 P380：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成（M0031），为双 Cl 桥连的双核 Cu 配合物（M0042）；与 KPF₆ 交换得 Cu-2-PF₆，再溶入 1 M LiTFSI＋2 wt% LiNO₃ 的 DME/DOL 中由 TFSI⁻ 置换得 Cu-2-T（M0040），为单 Cl 桥连的双核 Cu 配合物（M0043，Figure 1a 晶体结构，CCDC 2243502）</t>
         </is>
       </c>
       <c r="Q44" s="1" t="inlineStr">
         <is>
-          <t>金属配合物，没有可靠的单一 SMILES，不算 RDKit 描述符，分析时按“含 Cu-2-T”分块记录。原文 P380：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成（M0031），为双 Cl 桥连的双核 Cu 配合物（M0042）；与 KPF₆ 交换得 Cu-2-PF₆，再溶入 1 M LiTFSI＋2 wt% LiNO₃ 的 DME/DOL 中由 TFSI⁻ 置换得 Cu-2-T（M0040），为单 Cl 桥连的双核 Cu 配合物（M0043，Figure 1a 晶体结构，CCDC 2243502）</t>
+          <t>金属配合物，整体没有可靠的单一 SMILES，整体不算 RDKit 描述符，配体 1,10-菲咯啉单独算；分析时按“含 Cu-2-T”分块记录。原文 P380：Cu-2 由 CuCl₂·2H₂O 与 1,10-菲咯啉按 1:1 合成（M0031），为双 Cl 桥连的双核 Cu 配合物（M0042）；与 KPF₆ 交换得 Cu-2-PF₆，再溶入 1 M LiTFSI＋2 wt% LiNO₃ 的 DME/DOL 中由 TFSI⁻ 置换得 Cu-2-T（M0040），为单 Cl 桥连的双核 Cu 配合物（M0043，Figure 1a 晶体结构，CCDC 2243502）</t>
         </is>
       </c>
     </row>
@@ -9165,12 +9256,12 @@
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0060 与 dimethyl tetrasulfide (DMTtS)、DMDS 并列为二甲基多硫醚中间体，S0005 把 DMTS 加入电解液测 ¹H NMR，判为二甲基三硫醚</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 6 篇里 6 篇指此物（100%，见缩写词典）；全文只写缩写；M0060 与 dimethyl tetrasulfide (DMTtS)、DMDS 并列为二甲基多硫醚中间体，S0005 把 DMTS 加入电解液测 ¹H NMR，判为二甲基三硫醚</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
@@ -9491,12 +9582,12 @@
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；原文 M0214 全称写作“1,2-dioxolane (DOL)”，位次有误：1,2-二氧戊环是另一种异构体（环状过氧化物），不作电解液溶剂；本篇其余各处都是“1 M LiTFSI in DOL/DME with 1 wt% LiNO3”标准醚类电解液（M0060、M0079、S0014），判为 1,3-二氧戊环</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 412 篇里 398 篇指此物（97%，见缩写词典）；原文 M0214 全称写作“1,2-dioxolane (DOL)”，位次有误：1,2-二氧戊环是另一种异构体（环状过氧化物），不作电解液溶剂；本篇其余各处都是“1 M LiTFSI in DOL/DME with 1 wt% LiNO3”标准醚类电解液（M0060、M0079、S0014），判为 1,3-二氧戊环</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
@@ -11758,12 +11849,12 @@
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；原文 M0024 写“1,2-dimethoxymethane (DME)”，这个名称不成立（甲烷只有一个碳，不会有 1,2 位）；M0025 写 DME 沸点 42 °C，这是二甲氧基甲烷（甲缩醛）的沸点，1,2-二甲氧基乙烷为 85 °C。但对照电解液是锂硫标准的“1 M LiTFSI/DOL+DME（1:1）”（S0008），M0048 引用的 Suo 等 7 M LiTFSI-DOL:DME 也是 1,2-二甲氧基乙烷，判为 1,2-二甲氧基乙烷</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 437 篇里 413 篇指此物（95%，见缩写词典）；原文 M0024 写“1,2-dimethoxymethane (DME)”，这个名称不成立（甲烷只有一个碳，不会有 1,2 位）；M0025 写 DME 沸点 42 °C，这是二甲氧基甲烷（甲缩醛）的沸点，1,2-二甲氧基乙烷为 85 °C。但对照电解液是锂硫标准的“1 M LiTFSI/DOL+DME（1:1）”（S0008），M0048 引用的 Suo 等 7 M LiTFSI-DOL:DME 也是 1,2-二甲氧基乙烷，判为 1,2-二甲氧基乙烷</t>
         </is>
       </c>
       <c r="J60" s="1" t="inlineStr">
@@ -14945,12 +15036,12 @@
       </c>
       <c r="H129" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；原文 M0169 写“1, 2-dimethoxythane (DME, Aladdin, 99.5 %)”，少一个 e，判为 1,2-二甲氧基乙烷</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 437 篇里 413 篇指此物（95%，见缩写词典）；原文 M0169 写“1, 2-dimethoxythane (DME, Aladdin, 99.5 %)”，少一个 e，判为 1,2-二甲氧基乙烷</t>
         </is>
       </c>
       <c r="J129" s="1" t="inlineStr">
@@ -15965,12 +16056,12 @@
       </c>
       <c r="H151" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I151" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；S0029 写 LiFSI 购自 Tansoole，M0174 写富 LiF 主要来自 LiFSI 盐，按双氟磺酰亚胺锂</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 100 篇里 99 篇指此物（99%，见缩写词典）；全文只写缩写；S0029 写 LiFSI 购自 Tansoole，M0174 写富 LiF 主要来自 LiFSI 盐，按双氟磺酰亚胺锂</t>
         </is>
       </c>
       <c r="J151" s="1" t="inlineStr">
@@ -18181,12 +18272,12 @@
       </c>
       <c r="H199" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I199" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0031 写常规碳酸酯电解液，M0069 中 DEC 与 EC、PF₆⁻ 并列，判为碳酸二乙酯</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 23 篇里 22 篇指此物（96%，见缩写词典）；全文只写缩写；M0031 写常规碳酸酯电解液，M0069 中 DEC 与 EC、PF₆⁻ 并列，判为碳酸二乙酯</t>
         </is>
       </c>
       <c r="J199" s="1" t="inlineStr">
@@ -18921,12 +19012,12 @@
       </c>
       <c r="H215" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 437 篇里 413 篇指此物（95%，见缩写词典）；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
         </is>
       </c>
       <c r="J215" s="1" t="inlineStr">
@@ -18971,12 +19062,12 @@
       </c>
       <c r="H216" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I216" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 412 篇里 398 篇指此物（97%，见缩写词典）；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
         </is>
       </c>
       <c r="J216" s="1" t="inlineStr">
@@ -19113,12 +19204,12 @@
       </c>
       <c r="H219" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I219" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 341 篇里 339 篇指此物（99%，见缩写词典）；全文只写缩写；M0074 写“conventional ether based electrolyte (i.e., 1 M LiTFSI in DME: DOL (1:1 v/v))”，即锂硫标准醚类电解液，按通用含义</t>
         </is>
       </c>
       <c r="J219" s="1" t="inlineStr">
@@ -19633,12 +19724,12 @@
       </c>
       <c r="H230" s="1" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I230" s="1" t="inlineStr">
         <is>
-          <t>本篇原文未找到全称；原文 M0047 全称写作“lithium bis(fluoromethanesulfonyl)imide (LiFSI; anhydrous, 98%, TCI)”，多了 methane（那是另一种结构）；缩写、TCI 商品和 M0190 的 FSI⁻ 都指双氟磺酰亚胺锂</t>
+          <t>本篇原文没有可用的全称；领域通用缩写：本地 670 篇文献中定义该缩写的 100 篇里 99 篇指此物（99%，见缩写词典）；原文 M0047 全称写作“lithium bis(fluoromethanesulfonyl)imide (LiFSI; anhydrous, 98%, TCI)”，多了 methane（那是另一种结构）；缩写、TCI 商品和 M0190 的 FSI⁻ 都指双氟磺酰亚胺锂</t>
         </is>
       </c>
       <c r="J230" s="1" t="inlineStr">
@@ -21520,7 +21611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB57"/>
+  <dimension ref="A1:AB58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27178,6 +27269,104 @@
         <v>0</v>
       </c>
       <c r="AB57" s="1" t="inlineStr">
+        <is>
+          <t>🧮</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>CU2T</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Cu-2-T（氯桥双核铜配合物）</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>配体（1,10-菲咯啉）</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>金属配合物</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>c1cnc2c(c1)ccc1cccnc12</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>180.21</v>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="1" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="P58" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="1" t="inlineStr">
         <is>
           <t>🧮</t>
         </is>

--- a/output/组分结构表_F版30篇_2026-10-31/组分结构表.xlsx
+++ b/output/组分结构表_F版30篇_2026-10-31/组分结构表.xlsx
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>同意按氧化还原介体归类：原文称“均相催化剂”，但 M0092 写明不含硫的电池 CV 有一对氧化还原峰，在硫反应电压窗口内有本征氧化还原活性，起的是介体作用，类别已改。它不是纯无机物，是 Cu(II) 与有机配体 1,10-菲咯啉的配合物，整体没有可靠的单一 SMILES。处理：拆成能算的部分——金属 Cu、价态、双核、单 Cl 桥、反离子 TFSI⁻ 记为类别特征；配体 1,10-菲咯啉单独算 RDKit 描述符（描述符页“配体”行，已与 PubChem 核对）。对介体来说比结构更直接的特征是氧化还原电位，P380 只在 Figure S11 给 CV 曲线、正文没有数值，建议列入待定由读图补。LiI、InI₃、LiBr 这类简单无机介体按离子写 SMILES 就能算，同样建议补氧化还原对与电位。</t>
+          <t>同意按氧化还原介体归类：原文称“均相催化剂”，但 M0092 写明不含硫的电池 CV 有一对氧化还原峰，在硫反应电压窗口内有本征氧化还原活性，起的是介体作用，类别已改。它不是纯无机物，是 Cu(II) 与有机配体 1,10-菲咯啉的配合物，整体没有可靠的单一 SMILES。处理：拆成能算的部分——金属 Cu、价态、双核、单 Cl 桥、反离子 TFSI⁻ 记为类别特征；配体 1,10-菲咯啉单独算 RDKit 描述符（描述符页“配体”行，已与 PubChem 核对）。对介体来说比结构更直接的特征是氧化还原电位，P380 只在 Figure S11 给 CV 曲线、正文没有数值。10-31 你定暂不做电位（介体类数据少、不是主要分析），配方中只记“含哪种介体”。LiI、InI₃、LiBr 这类简单无机介体按离子写 SMILES 就能算。</t>
         </is>
       </c>
     </row>
